--- a/assets/floor_2_data.xlsx
+++ b/assets/floor_2_data.xlsx
@@ -526,7 +526,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -553,19 +553,19 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>WIFI-AP-Lobby</v>
+        <v>FACTHCHOVM001</v>
       </c>
       <c r="B2" t="str">
-        <v>AP</v>
+        <v>Server</v>
       </c>
       <c r="C2">
-        <v>-800</v>
+        <v>2201</v>
       </c>
       <c r="D2">
-        <v>1200</v>
+        <v>-564</v>
       </c>
       <c r="E2" t="str">
-        <v>Main entrance access point</v>
+        <v>Domain Controller 1</v>
       </c>
       <c r="F2" t="str">
         <v>Active</v>
@@ -576,19 +576,19 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>WIFI-AP-Canteen</v>
+        <v>FACTHCHOVM002</v>
       </c>
       <c r="B3" t="str">
-        <v>AP</v>
+        <v>Server</v>
       </c>
       <c r="C3">
-        <v>550</v>
+        <v>2203</v>
       </c>
       <c r="D3">
-        <v>900</v>
+        <v>-522</v>
       </c>
       <c r="E3" t="str">
-        <v>Cafeteria coverage</v>
+        <v>File Server 1</v>
       </c>
       <c r="F3" t="str">
         <v>Active</v>
@@ -599,19 +599,19 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SRV-DC-01</v>
+        <v>THMJNCHOTH01S01</v>
       </c>
       <c r="B4" t="str">
-        <v>Server</v>
+        <v>Switch</v>
       </c>
       <c r="C4">
-        <v>-1500</v>
+        <v>2256</v>
       </c>
       <c r="D4">
-        <v>-1300</v>
+        <v>-521</v>
       </c>
       <c r="E4" t="str">
-        <v>Domain Controller 1</v>
+        <v>Main Distribution Frame Switch</v>
       </c>
       <c r="F4" t="str">
         <v>Active</v>
@@ -622,19 +622,19 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SRV-FS-01</v>
+        <v>THMJNCHOTH01S08</v>
       </c>
       <c r="B5" t="str">
-        <v>Server</v>
+        <v>Switch</v>
       </c>
       <c r="C5">
-        <v>-1550</v>
+        <v>2256</v>
       </c>
       <c r="D5">
-        <v>-1300</v>
+        <v>-567</v>
       </c>
       <c r="E5" t="str">
-        <v>File Server 1</v>
+        <v>Main Distribution Frame Switch</v>
       </c>
       <c r="F5" t="str">
         <v>Active</v>
@@ -645,16 +645,16 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SW-IDF-01</v>
+        <v>NEW Switch</v>
       </c>
       <c r="B6" t="str">
         <v>Switch</v>
       </c>
       <c r="C6">
-        <v>-1450</v>
+        <v>722</v>
       </c>
       <c r="D6">
-        <v>-1350</v>
+        <v>-287</v>
       </c>
       <c r="E6" t="str">
         <v>Main Distribution Frame Switch</v>
@@ -666,9 +666,354 @@
         <v/>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>AP-017</v>
+      </c>
+      <c r="B7" t="str">
+        <v>AP</v>
+      </c>
+      <c r="C7">
+        <v>-1637</v>
+      </c>
+      <c r="D7">
+        <v>-19</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Main entrance access point</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Active</v>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>AP-018</v>
+      </c>
+      <c r="B8" t="str">
+        <v>AP</v>
+      </c>
+      <c r="C8">
+        <v>-1636</v>
+      </c>
+      <c r="D8">
+        <v>462</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Cafeteria coverage</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Active</v>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>AP-019</v>
+      </c>
+      <c r="B9" t="str">
+        <v>AP</v>
+      </c>
+      <c r="C9">
+        <v>-1148</v>
+      </c>
+      <c r="D9">
+        <v>507</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v>Active</v>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>AP-020</v>
+      </c>
+      <c r="B10" t="str">
+        <v>AP</v>
+      </c>
+      <c r="C10">
+        <v>-1153</v>
+      </c>
+      <c r="D10">
+        <v>37</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v>Active</v>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>AP-021</v>
+      </c>
+      <c r="B11" t="str">
+        <v>AP</v>
+      </c>
+      <c r="C11">
+        <v>-949</v>
+      </c>
+      <c r="D11">
+        <v>438</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v>Active</v>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>AP-022</v>
+      </c>
+      <c r="B12" t="str">
+        <v>AP</v>
+      </c>
+      <c r="C12">
+        <v>-659</v>
+      </c>
+      <c r="D12">
+        <v>678</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v>Active</v>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>AP-023</v>
+      </c>
+      <c r="B13" t="str">
+        <v>AP</v>
+      </c>
+      <c r="C13">
+        <v>-318</v>
+      </c>
+      <c r="D13">
+        <v>593</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v>Active</v>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>AP-024</v>
+      </c>
+      <c r="B14" t="str">
+        <v>AP</v>
+      </c>
+      <c r="C14">
+        <v>-541</v>
+      </c>
+      <c r="D14">
+        <v>-1239</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v>Active</v>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>AP-025</v>
+      </c>
+      <c r="B15" t="str">
+        <v>AP</v>
+      </c>
+      <c r="C15">
+        <v>462</v>
+      </c>
+      <c r="D15">
+        <v>-58</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v>Active</v>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>AP-026</v>
+      </c>
+      <c r="B16" t="str">
+        <v>AP</v>
+      </c>
+      <c r="C16">
+        <v>703</v>
+      </c>
+      <c r="D16">
+        <v>-1144</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v>Active</v>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>AP-027</v>
+      </c>
+      <c r="B17" t="str">
+        <v>AP</v>
+      </c>
+      <c r="C17">
+        <v>974</v>
+      </c>
+      <c r="D17">
+        <v>-757</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v>Active</v>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>AP-028</v>
+      </c>
+      <c r="B18" t="str">
+        <v>AP</v>
+      </c>
+      <c r="C18">
+        <v>1281</v>
+      </c>
+      <c r="D18">
+        <v>-1262</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v>Active</v>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>AP-029</v>
+      </c>
+      <c r="B19" t="str">
+        <v>AP</v>
+      </c>
+      <c r="C19">
+        <v>1460</v>
+      </c>
+      <c r="D19">
+        <v>-495</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v>Active</v>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>AP-030</v>
+      </c>
+      <c r="B20" t="str">
+        <v>AP</v>
+      </c>
+      <c r="C20">
+        <v>2238</v>
+      </c>
+      <c r="D20">
+        <v>-246</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v>Active</v>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>AP-031</v>
+      </c>
+      <c r="B21" t="str">
+        <v>AP</v>
+      </c>
+      <c r="C21">
+        <v>2399</v>
+      </c>
+      <c r="D21">
+        <v>-910</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v>Active</v>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G21"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/assets/floor_2_data.xlsx
+++ b/assets/floor_2_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\M.Mead\5.FactoryView\assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\M.Mead\9.FactoryView\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26056B3B-F7B9-4D6E-93E1-79729B5DA7FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A19E66D0-D9BF-4C51-9CED-E7D7856C2467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="147">
   <si>
     <t>Name</t>
   </si>
@@ -244,13 +244,238 @@
   </si>
   <si>
     <t>Salmon</t>
+  </si>
+  <si>
+    <t>IP Address</t>
+  </si>
+  <si>
+    <t>MAC Address</t>
+  </si>
+  <si>
+    <t>Platform</t>
+  </si>
+  <si>
+    <t>Serial Number</t>
+  </si>
+  <si>
+    <t>Switch Detail</t>
+  </si>
+  <si>
+    <t>Port Details</t>
+  </si>
+  <si>
+    <t>10.198.85.164</t>
+  </si>
+  <si>
+    <t>f8:14:dd:9e:d1:40</t>
+  </si>
+  <si>
+    <t>CW9176I</t>
+  </si>
+  <si>
+    <t>WVN29460P4N</t>
+  </si>
+  <si>
+    <t>10.198.85.157</t>
+  </si>
+  <si>
+    <t>f8:14:dd:a2:57:a0</t>
+  </si>
+  <si>
+    <t>WVN29470BQ8</t>
+  </si>
+  <si>
+    <t>10.198.85.156</t>
+  </si>
+  <si>
+    <t>f8:14:dd:a2:5e:c0</t>
+  </si>
+  <si>
+    <t>WVN29470BRX</t>
+  </si>
+  <si>
+    <t>10.198.85.158</t>
+  </si>
+  <si>
+    <t>f8:14:dd:a2:53:40</t>
+  </si>
+  <si>
+    <t>WVN29470BP7</t>
+  </si>
+  <si>
+    <t>10.198.85.170</t>
+  </si>
+  <si>
+    <t>f8:14:dd:a2:64:60</t>
+  </si>
+  <si>
+    <t>WVN29470BT8</t>
+  </si>
+  <si>
+    <t>10.198.85.166</t>
+  </si>
+  <si>
+    <t>f8:14:dd:a2:5d:40</t>
+  </si>
+  <si>
+    <t>WVN29470BRK</t>
+  </si>
+  <si>
+    <t>10.198.85.171</t>
+  </si>
+  <si>
+    <t>f8:14:dd:a2:65:e0</t>
+  </si>
+  <si>
+    <t>WVN29470BTL</t>
+  </si>
+  <si>
+    <t>10.198.85.165</t>
+  </si>
+  <si>
+    <t>f8:14:dd:a2:5c:20</t>
+  </si>
+  <si>
+    <t>WVN29470BRA</t>
+  </si>
+  <si>
+    <t>10.198.85.169</t>
+  </si>
+  <si>
+    <t>f8:14:dd:a2:53:00</t>
+  </si>
+  <si>
+    <t>WVN29470BP5</t>
+  </si>
+  <si>
+    <t>10.198.85.172</t>
+  </si>
+  <si>
+    <t>f8:14:dd:9e:bc:20</t>
+  </si>
+  <si>
+    <t>WVN29460NZP</t>
+  </si>
+  <si>
+    <t>10.198.85.174</t>
+  </si>
+  <si>
+    <t>f8:14:dd:a2:51:60</t>
+  </si>
+  <si>
+    <t>WVN29470BNS</t>
+  </si>
+  <si>
+    <t>10.198.85.173</t>
+  </si>
+  <si>
+    <t>f8:14:dd:a2:58:20</t>
+  </si>
+  <si>
+    <t>WVN29470BQC</t>
+  </si>
+  <si>
+    <t>10.198.85.168</t>
+  </si>
+  <si>
+    <t>f8:14:dd:a2:84:80</t>
+  </si>
+  <si>
+    <t>WVN29470C0T</t>
+  </si>
+  <si>
+    <t>10.198.85.167</t>
+  </si>
+  <si>
+    <t>f8:14:dd:a2:81:60</t>
+  </si>
+  <si>
+    <t>WVN29470C02</t>
+  </si>
+  <si>
+    <t>10.198.85.175</t>
+  </si>
+  <si>
+    <t>f8:14:dd:a2:65:00</t>
+  </si>
+  <si>
+    <t>WVN29470BTD</t>
+  </si>
+  <si>
+    <t>THJMNMCHOTH01S04</t>
+  </si>
+  <si>
+    <t>Gi2/0/10</t>
+  </si>
+  <si>
+    <t>Gi2/0/11</t>
+  </si>
+  <si>
+    <t>Gi2/0/12</t>
+  </si>
+  <si>
+    <t>Gi2/0/13</t>
+  </si>
+  <si>
+    <t>Gi2/0/14</t>
+  </si>
+  <si>
+    <t>Gi2/0/15</t>
+  </si>
+  <si>
+    <t>G1/0/20</t>
+  </si>
+  <si>
+    <t>THCHON-CCB-AS10</t>
+  </si>
+  <si>
+    <t>G1/0/21</t>
+  </si>
+  <si>
+    <t>G1/0/22</t>
+  </si>
+  <si>
+    <t>G1/0/23</t>
+  </si>
+  <si>
+    <t>G1/0/24</t>
+  </si>
+  <si>
+    <t>G1/0/25</t>
+  </si>
+  <si>
+    <t>Gi1/0/34</t>
+  </si>
+  <si>
+    <t>THJMNMCHOTH01S02</t>
+  </si>
+  <si>
+    <t>Gi1/0/35</t>
+  </si>
+  <si>
+    <t>G1/0/10</t>
+  </si>
+  <si>
+    <t>AP-032</t>
+  </si>
+  <si>
+    <t>10.198.85.178</t>
+  </si>
+  <si>
+    <t>f8:14:dd:a2:6c:a0</t>
+  </si>
+  <si>
+    <t>WVN29470BV6</t>
+  </si>
+  <si>
+    <t>G1/0/11</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -258,16 +483,41 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -275,12 +525,43 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -621,9 +902,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -649,7 +930,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -675,7 +956,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -701,7 +982,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -727,7 +1008,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -763,10 +1044,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H24"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="18.44140625" customWidth="1"/>
+    <col min="5" max="5" width="29" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -791,8 +1082,26 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="I1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -818,7 +1127,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -844,7 +1153,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -870,7 +1179,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -896,9 +1205,9 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>132</v>
       </c>
       <c r="B6" t="s">
         <v>28</v>
@@ -910,7 +1219,7 @@
         <v>-287</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F6" t="s">
         <v>11</v>
@@ -922,7 +1231,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -948,7 +1257,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -974,7 +1283,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>37</v>
       </c>
@@ -999,8 +1308,26 @@
       <c r="H9" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="I9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="M9" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="N9" s="7" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>39</v>
       </c>
@@ -1025,8 +1352,26 @@
       <c r="H10" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="I10" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="N10" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -1051,8 +1396,26 @@
       <c r="H11" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="I11" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>41</v>
       </c>
@@ -1077,8 +1440,26 @@
       <c r="H12" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="I12" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="N12" s="7" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>42</v>
       </c>
@@ -1103,8 +1484,26 @@
       <c r="H13" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="I13" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>43</v>
       </c>
@@ -1129,8 +1528,26 @@
       <c r="H14" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="I14" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>44</v>
       </c>
@@ -1155,8 +1572,26 @@
       <c r="H15" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="I15" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="M15" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="N15" s="9" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>45</v>
       </c>
@@ -1181,8 +1616,26 @@
       <c r="H16" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="I16" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>46</v>
       </c>
@@ -1207,8 +1660,26 @@
       <c r="H17" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="I17" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="M17" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="N17" s="7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>47</v>
       </c>
@@ -1233,8 +1704,26 @@
       <c r="H18" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="I18" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="N18" s="7" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>48</v>
       </c>
@@ -1259,8 +1748,26 @@
       <c r="H19" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="I19" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="M19" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="N19" s="7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>49</v>
       </c>
@@ -1285,8 +1792,26 @@
       <c r="H20" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="I20" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="M20" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="N20" s="7" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>50</v>
       </c>
@@ -1311,8 +1836,26 @@
       <c r="H21" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="I21" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="M21" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="N21" s="9" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1337,8 +1880,26 @@
       <c r="H22" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="I22" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="M22" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="N22" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>52</v>
       </c>
@@ -1363,37 +1924,93 @@
       <c r="H23" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="I23" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="M23" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="N23" s="9" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="B24" t="s">
         <v>38</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="10">
+        <v>-428</v>
+      </c>
+      <c r="D24" s="10">
+        <v>1394</v>
+      </c>
+      <c r="F24" t="s">
+        <v>11</v>
+      </c>
+      <c r="H24" t="s">
+        <v>32</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="M24" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="N24" s="7" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25">
         <v>-2261</v>
       </c>
-      <c r="D24">
+      <c r="D25">
         <v>927</v>
       </c>
-      <c r="E24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" t="s">
-        <v>11</v>
-      </c>
-      <c r="G24" t="s">
-        <v>12</v>
-      </c>
-      <c r="H24" t="s">
+      <c r="E25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" t="s">
+        <v>11</v>
+      </c>
+      <c r="G25" t="s">
+        <v>12</v>
+      </c>
+      <c r="H25" t="s">
         <v>71</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:H23 A24:G24" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:H5 A25:G25 A7:H23 B6:D6 F6:H6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1401,9 +2018,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1429,7 +2046,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>54</v>
       </c>
@@ -1455,7 +2072,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>57</v>
       </c>
@@ -1481,7 +2098,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>60</v>
       </c>
@@ -1518,9 +2135,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1546,7 +2163,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>63</v>
       </c>
@@ -1572,7 +2189,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>66</v>
       </c>
@@ -1598,7 +2215,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>69</v>
       </c>

--- a/assets/floor_2_data.xlsx
+++ b/assets/floor_2_data.xlsx
@@ -8,18 +8,30 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\M.Mead\9.FactoryView\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF6D720C-6277-4D78-8F81-7163397DC649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E1CDBD-03BB-4540-8588-84395B5C352A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="loc_name" sheetId="1" r:id="rId1"/>
     <sheet name="it_dev" sheetId="2" r:id="rId2"/>
-    <sheet name="weight" sheetId="6" r:id="rId3"/>
-    <sheet name="zones" sheetId="5" r:id="rId4"/>
+    <sheet name="prod_comp" sheetId="9" r:id="rId3"/>
+    <sheet name="machine" sheetId="8" r:id="rId4"/>
+    <sheet name="weight" sheetId="6" r:id="rId5"/>
+    <sheet name="zones" sheetId="5" r:id="rId6"/>
+    <sheet name="flow" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -28,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="229">
   <si>
     <t>Name</t>
   </si>
@@ -489,23 +501,239 @@
     <t>Digital Scale</t>
   </si>
   <si>
-    <t>Vitamin C</t>
-  </si>
-  <si>
-    <t>Vitamin B</t>
-  </si>
-  <si>
-    <t>Analog Scale</t>
-  </si>
-  <si>
-    <t>Vitamin A</t>
+    <t>Points</t>
+  </si>
+  <si>
+    <t>Speed</t>
+  </si>
+  <si>
+    <t>DashSize</t>
+  </si>
+  <si>
+    <t>GapSize</t>
+  </si>
+  <si>
+    <t>Tension</t>
+  </si>
+  <si>
+    <t>Shape</t>
+  </si>
+  <si>
+    <t>ShowLine</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Tipping-&gt;BlenderA</t>
+  </si>
+  <si>
+    <t>1080,-681;1103,-630;1102,-583;1035,-519</t>
+  </si>
+  <si>
+    <t>#ff6600</t>
+  </si>
+  <si>
+    <t>powder</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Tipping-&gt;BlenderB</t>
+  </si>
+  <si>
+    <t>1106,-682;1104,-602;1048,-560;957,-535;944,-519</t>
+  </si>
+  <si>
+    <t>Tipping-&gt;BlenderC</t>
+  </si>
+  <si>
+    <t>1069,-681;1069,-611;1040,-572;852,-569;807,-542;807,-507</t>
+  </si>
+  <si>
+    <t>Tipping-&gt;BlenderD</t>
+  </si>
+  <si>
+    <t>1068,-680;1065,-601;1037,-574;716,-574;656,-539;662,-521</t>
+  </si>
+  <si>
+    <t>BlenderA-&gt;P2</t>
+  </si>
+  <si>
+    <t>BlenderA-&gt;P3</t>
+  </si>
+  <si>
+    <t>BlenderD-&gt;P1</t>
+  </si>
+  <si>
+    <t>BlenderB-&gt;P1</t>
+  </si>
+  <si>
+    <t>BlenderC-&gt;P4</t>
+  </si>
+  <si>
+    <t>BlenderB-&gt;Can</t>
+  </si>
+  <si>
+    <t>BlenderC-&gt;Can</t>
+  </si>
+  <si>
+    <t>#39630f</t>
+  </si>
+  <si>
+    <t>#2eb36a</t>
+  </si>
+  <si>
+    <t>1050,-519;1140,-527;1383,-530;1448,-577;1448,-577,-100</t>
+  </si>
+  <si>
+    <t>1038,-518;1130,-508;1295,-511;1446,-409;1446,-409,-100</t>
+  </si>
+  <si>
+    <t>664,-514;662,-464;1135,-459;1139,-643;1181,-680;1276,-680;1357,-672;1387,-694;1449,-703;1449,-703,-100</t>
+  </si>
+  <si>
+    <t>944,-524;945,-573;1055,-574;1092,-615;1155,-695;1281,-697;1353,-696;1465,-706;1465,-706,-100</t>
+  </si>
+  <si>
+    <t>811,-505;864,-573;1056,-576;1157,-696;1282,-699;1353,-686;1366,-649;1366,-332;1408,-293;1460,-291;1470,-307;1470,-307,-100</t>
+  </si>
+  <si>
+    <t>947,-518;987,-572;1138,-570;1135,-399;1175,-359;1185,-300;1185,-227;1154,-145;1154,-145,-100</t>
+  </si>
+  <si>
+    <t>810,-509;839,-574;1138,-568;1132,-397;1175,-368;1182,-296;1181,-238;1151,-220;1137,-195;1137,-195,-100</t>
+  </si>
+  <si>
+    <t>Machine</t>
+  </si>
+  <si>
+    <t>2026-04-13</t>
+  </si>
+  <si>
+    <t>Blend-A</t>
+  </si>
+  <si>
+    <t>Blend-B</t>
+  </si>
+  <si>
+    <t>Blend-C</t>
+  </si>
+  <si>
+    <t>Blend-D</t>
+  </si>
+  <si>
+    <t>Scale</t>
+  </si>
+  <si>
+    <t>2026-04-14</t>
+  </si>
+  <si>
+    <t>Vintamin IN</t>
+  </si>
+  <si>
+    <t>sack</t>
+  </si>
+  <si>
+    <t>Vitamin R#1</t>
+  </si>
+  <si>
+    <t>680,-919;685,-883;836,-876;837,-922;859,-873;901,-797;903,-752;966,-748;968,-624</t>
+  </si>
+  <si>
+    <t>Vitamin R#2</t>
+  </si>
+  <si>
+    <t>678,-926;672,-885;981,-885;981,-918;1021,-886;1135,-799;1133,-759;968,-747;969,-627</t>
+  </si>
+  <si>
+    <t>Vitamin R#3</t>
+  </si>
+  <si>
+    <t>688,-919;679,-872;1202,-873;1205,-912;1249,-870;1198,-798;1189,-756;970,-750;968,-628</t>
+  </si>
+  <si>
+    <t>Vitamin R#4</t>
+  </si>
+  <si>
+    <t>682,-925;675,-871;882,-870;909,-779;1348,-768;1346,-973;1299,-1008;1313,-1044;1372,-970;1358,-733;967,-746;954,-628</t>
+  </si>
+  <si>
+    <t>#fca92b</t>
+  </si>
+  <si>
+    <t>#fac887</t>
+  </si>
+  <si>
+    <t>#fac888</t>
+  </si>
+  <si>
+    <t>#fac889</t>
+  </si>
+  <si>
+    <t>#fac890</t>
+  </si>
+  <si>
+    <t>404,-661,-100;404,-661;546,-659;554,-930;680,-935</t>
+  </si>
+  <si>
+    <t>GWINS</t>
+  </si>
+  <si>
+    <t>2025-12-15</t>
+  </si>
+  <si>
+    <t>S&amp;T</t>
+  </si>
+  <si>
+    <t>#767dde</t>
+  </si>
+  <si>
+    <t>Gw-b-1</t>
+  </si>
+  <si>
+    <t>Gw-b-2</t>
+  </si>
+  <si>
+    <t>Gw-b-3</t>
+  </si>
+  <si>
+    <t>Gw-b-4</t>
+  </si>
+  <si>
+    <t>S&amp;T-b-1</t>
+  </si>
+  <si>
+    <t>S&amp;T-b-2</t>
+  </si>
+  <si>
+    <t>S&amp;T-b-3</t>
+  </si>
+  <si>
+    <t>S&amp;T-b-4</t>
+  </si>
+  <si>
+    <t>Gw-d-1</t>
+  </si>
+  <si>
+    <t>Gw-v-2</t>
+  </si>
+  <si>
+    <t>Gw-v-1</t>
+  </si>
+  <si>
+    <t>Gw-v-3</t>
+  </si>
+  <si>
+    <t>Gw-v-4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -516,6 +744,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -931,7 +1165,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
@@ -1005,61 +1239,6 @@
       </c>
       <c r="D5">
         <v>-233</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C6">
-        <v>1467</v>
-      </c>
-      <c r="D6">
-        <v>-706</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>148</v>
-      </c>
-      <c r="C7" s="10">
-        <v>1467</v>
-      </c>
-      <c r="D7">
-        <v>-572</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="C8" s="10">
-        <v>1467</v>
-      </c>
-      <c r="D8">
-        <v>-417</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="C9" s="10">
-        <v>1467</v>
-      </c>
-      <c r="D9">
-        <v>-305</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>146</v>
-      </c>
-      <c r="C10">
-        <v>1142</v>
-      </c>
-      <c r="D10">
-        <v>-168</v>
       </c>
     </row>
   </sheetData>
@@ -1937,11 +2116,13 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A113FB90-F9A2-4A63-A07C-A429C0E9DE7B}">
-  <dimension ref="A1:H4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77B569B9-40DE-442E-B3B4-88A1EBBBE413}">
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="8.88671875" style="10"/>
+    <col min="1" max="6" width="8.88671875" style="10"/>
+    <col min="7" max="7" width="10.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
@@ -1972,16 +2153,16 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
-        <v>156</v>
+        <v>216</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>155</v>
+        <v>212</v>
       </c>
       <c r="C2" s="10">
-        <v>1280</v>
+        <v>1000</v>
       </c>
       <c r="D2" s="10">
-        <v>-343</v>
+        <v>-600</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>151</v>
@@ -1989,19 +2170,342 @@
       <c r="F2" s="10" t="s">
         <v>8</v>
       </c>
+      <c r="G2" s="10" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
-        <v>154</v>
+        <v>217</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>152</v>
+        <v>212</v>
       </c>
       <c r="C3" s="10">
-        <v>1289</v>
+        <v>900</v>
       </c>
       <c r="D3" s="10">
-        <v>-243</v>
+        <v>-600</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="C4" s="10">
+        <v>825</v>
+      </c>
+      <c r="D4" s="10">
+        <v>-600</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="C5" s="10">
+        <v>700</v>
+      </c>
+      <c r="D5" s="10">
+        <v>-600</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="C6" s="10">
+        <v>1020</v>
+      </c>
+      <c r="D6" s="10">
+        <v>-575</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="C7" s="10">
+        <v>920</v>
+      </c>
+      <c r="D7" s="10">
+        <v>-575</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="C8" s="10">
+        <v>845</v>
+      </c>
+      <c r="D8" s="10">
+        <v>-575</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="C9" s="10">
+        <v>720</v>
+      </c>
+      <c r="D9" s="10">
+        <v>-575</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="C10" s="10">
+        <v>673</v>
+      </c>
+      <c r="D10" s="10">
+        <v>-941</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="C11" s="10">
+        <v>897</v>
+      </c>
+      <c r="D11" s="10">
+        <v>-940</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="C12" s="10">
+        <v>1135</v>
+      </c>
+      <c r="D12" s="10">
+        <v>-935</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="C13" s="10">
+        <v>1240</v>
+      </c>
+      <c r="D13" s="10">
+        <v>-934</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="C14" s="10">
+        <v>1350</v>
+      </c>
+      <c r="D14" s="10">
+        <v>-1050</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9DA2CD0-4EB4-4612-8E4D-C2326FA17524}">
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="19.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="8.88671875" style="10"/>
+    <col min="5" max="5" width="15.109375" style="10" customWidth="1"/>
+    <col min="6" max="6" width="8.88671875" style="10"/>
+    <col min="7" max="7" width="12.44140625" style="10" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="C2" s="10">
+        <v>1019</v>
+      </c>
+      <c r="D2" s="10">
+        <v>-504</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="C3" s="10">
+        <v>914</v>
+      </c>
+      <c r="D3" s="10">
+        <v>-504</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>151</v>
@@ -2009,25 +2513,124 @@
       <c r="F3" s="10" t="s">
         <v>8</v>
       </c>
+      <c r="G3" s="10" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
-        <v>153</v>
+        <v>192</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>152</v>
+        <v>188</v>
       </c>
       <c r="C4" s="10">
-        <v>1349</v>
+        <v>798</v>
       </c>
       <c r="D4" s="10">
-        <v>-130</v>
+        <v>-504</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>151</v>
       </c>
       <c r="F4" s="10" t="s">
         <v>8</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="C5" s="10">
+        <v>653</v>
+      </c>
+      <c r="D5" s="10">
+        <v>-501</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="C6">
+        <v>1467</v>
+      </c>
+      <c r="D6">
+        <v>-706</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>148</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="C7" s="10">
+        <v>1467</v>
+      </c>
+      <c r="D7">
+        <v>-572</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="C8" s="10">
+        <v>1467</v>
+      </c>
+      <c r="D8">
+        <v>-417</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="C9" s="10">
+        <v>1467</v>
+      </c>
+      <c r="D9">
+        <v>-305</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>146</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="C10">
+        <v>1142</v>
+      </c>
+      <c r="D10">
+        <v>-168</v>
       </c>
     </row>
   </sheetData>
@@ -2035,7 +2638,188 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A113FB90-F9A2-4A63-A07C-A429C0E9DE7B}">
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="10"/>
+    <col min="2" max="2" width="10.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="8.88671875" style="10"/>
+    <col min="7" max="7" width="14.6640625" style="10" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C2" s="10">
+        <v>713</v>
+      </c>
+      <c r="D2" s="10">
+        <v>-930</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C3" s="10">
+        <v>857</v>
+      </c>
+      <c r="D3" s="10">
+        <v>-928</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C4" s="10">
+        <v>985</v>
+      </c>
+      <c r="D4" s="10">
+        <v>-922</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C5" s="10">
+        <v>1095</v>
+      </c>
+      <c r="D5" s="10">
+        <v>-922</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C6" s="10">
+        <v>1200</v>
+      </c>
+      <c r="D6" s="10">
+        <v>-922</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C7" s="10">
+        <v>1311</v>
+      </c>
+      <c r="D7" s="10">
+        <v>-1038</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>195</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -2480,4 +3264,534 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4FA26C3-CAFB-4728-933F-28CE0AA88343}">
+  <dimension ref="A1:J17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="16.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="112" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.44140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="7.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.88671875" style="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="D2" s="10">
+        <v>2</v>
+      </c>
+      <c r="E2" s="10">
+        <v>30</v>
+      </c>
+      <c r="F2" s="10">
+        <v>15</v>
+      </c>
+      <c r="G2" s="10">
+        <v>0</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="I2" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="D3" s="10">
+        <v>2</v>
+      </c>
+      <c r="E3" s="10">
+        <v>30</v>
+      </c>
+      <c r="F3" s="10">
+        <v>15</v>
+      </c>
+      <c r="G3" s="10">
+        <v>0</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="I3" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="D4" s="10">
+        <v>2</v>
+      </c>
+      <c r="E4" s="10">
+        <v>30</v>
+      </c>
+      <c r="F4" s="10">
+        <v>15</v>
+      </c>
+      <c r="G4" s="10">
+        <v>0</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="I4" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="D5" s="10">
+        <v>2</v>
+      </c>
+      <c r="E5" s="10">
+        <v>30</v>
+      </c>
+      <c r="F5" s="10">
+        <v>15</v>
+      </c>
+      <c r="G5" s="10">
+        <v>0</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="I5" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="D6" s="10">
+        <v>2</v>
+      </c>
+      <c r="E6" s="10">
+        <v>30</v>
+      </c>
+      <c r="F6" s="10">
+        <v>15</v>
+      </c>
+      <c r="G6" s="10">
+        <v>0</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="I6" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="D7" s="10">
+        <v>2</v>
+      </c>
+      <c r="E7" s="10">
+        <v>30</v>
+      </c>
+      <c r="F7" s="10">
+        <v>15</v>
+      </c>
+      <c r="G7" s="10">
+        <v>0</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="I7" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="D8" s="10">
+        <v>2</v>
+      </c>
+      <c r="E8" s="10">
+        <v>30</v>
+      </c>
+      <c r="F8" s="10">
+        <v>15</v>
+      </c>
+      <c r="G8" s="10">
+        <v>0</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="I8" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="D9" s="10">
+        <v>2</v>
+      </c>
+      <c r="E9" s="10">
+        <v>30</v>
+      </c>
+      <c r="F9" s="10">
+        <v>15</v>
+      </c>
+      <c r="G9" s="10">
+        <v>0</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="I9" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="D10" s="10">
+        <v>2</v>
+      </c>
+      <c r="E10" s="10">
+        <v>30</v>
+      </c>
+      <c r="F10" s="10">
+        <v>15</v>
+      </c>
+      <c r="G10" s="10">
+        <v>0</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="I10" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D11" s="10">
+        <v>2</v>
+      </c>
+      <c r="E11" s="10">
+        <v>30</v>
+      </c>
+      <c r="F11" s="10">
+        <v>15</v>
+      </c>
+      <c r="G11" s="10">
+        <v>0</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="I11" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D12" s="10">
+        <v>2</v>
+      </c>
+      <c r="E12" s="10">
+        <v>30</v>
+      </c>
+      <c r="F12" s="10">
+        <v>15</v>
+      </c>
+      <c r="G12" s="10">
+        <v>0</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="I12" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="D13" s="10">
+        <v>1</v>
+      </c>
+      <c r="E13" s="10">
+        <v>20</v>
+      </c>
+      <c r="F13" s="10">
+        <v>5</v>
+      </c>
+      <c r="G13" s="10">
+        <v>0</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="I13" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="D14" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="E14" s="10">
+        <v>20</v>
+      </c>
+      <c r="F14" s="10">
+        <v>5</v>
+      </c>
+      <c r="G14" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="I14" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="D15" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="E15" s="10">
+        <v>20</v>
+      </c>
+      <c r="F15" s="10">
+        <v>5</v>
+      </c>
+      <c r="G15" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="I15" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A16" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="D16" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="10">
+        <v>20</v>
+      </c>
+      <c r="F16" s="10">
+        <v>5</v>
+      </c>
+      <c r="G16" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="I16" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A17" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="D17" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="E17" s="10">
+        <v>20</v>
+      </c>
+      <c r="F17" s="10">
+        <v>5</v>
+      </c>
+      <c r="G17" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="I17" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/assets/floor_2_data.xlsx
+++ b/assets/floor_2_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\M.Mead\9.FactoryView\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E1CDBD-03BB-4540-8588-84395B5C352A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FECEA1C3-9BBC-41C5-B7E8-390A2A341868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="loc_name" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,8 @@
     <sheet name="machine" sheetId="8" r:id="rId4"/>
     <sheet name="weight" sheetId="6" r:id="rId5"/>
     <sheet name="zones" sheetId="5" r:id="rId6"/>
-    <sheet name="flow" sheetId="7" r:id="rId7"/>
+    <sheet name="flow_pouch" sheetId="7" r:id="rId7"/>
+    <sheet name="flow_can" sheetId="10" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,8 +40,51 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{E3A6C44F-CEB7-4D99-BFB7-0672FFB3BF06}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>User:
+Add Tension column to the flow sheet (0 to 1, default 0.5)
+0.0 = very round curves at corners (more organic)
+0.5 = balanced (default)
+1.0 = nearly straight lines between waypoints</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{3B8A1F74-2970-47B3-BF1B-B24AF6E7BF17}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>User:
+box, small_box, can, sack, powder</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="229">
   <si>
     <t>Name</t>
   </si>
@@ -3268,7 +3312,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4FA26C3-CAFB-4728-933F-28CE0AA88343}">
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.21875" style="10" bestFit="1" customWidth="1"/>
@@ -3589,28 +3633,28 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>186</v>
+        <v>211</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="D11" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" s="10">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F11" s="10">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G11" s="10">
         <v>0</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>164</v>
+        <v>197</v>
       </c>
       <c r="I11" s="10" t="b">
         <v>1</v>
@@ -3618,28 +3662,28 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>179</v>
+        <v>207</v>
       </c>
       <c r="D12" s="10">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="E12" s="10">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F12" s="10">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G12" s="10">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>164</v>
+        <v>197</v>
       </c>
       <c r="I12" s="10" t="b">
         <v>1</v>
@@ -3647,16 +3691,16 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D13" s="10">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E13" s="10">
         <v>20</v>
@@ -3665,7 +3709,7 @@
         <v>5</v>
       </c>
       <c r="G13" s="10">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H13" s="10" t="s">
         <v>197</v>
@@ -3676,13 +3720,13 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D14" s="10">
         <v>0.5</v>
@@ -3705,13 +3749,13 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D15" s="10">
         <v>0.5</v>
@@ -3729,64 +3773,6 @@
         <v>197</v>
       </c>
       <c r="I15" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A16" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="D16" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="E16" s="10">
-        <v>20</v>
-      </c>
-      <c r="F16" s="10">
-        <v>5</v>
-      </c>
-      <c r="G16" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="H16" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="I16" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A17" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="D17" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="E17" s="10">
-        <v>20</v>
-      </c>
-      <c r="F17" s="10">
-        <v>5</v>
-      </c>
-      <c r="G17" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="I17" s="10" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3794,4 +3780,105 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AC33B8A-E190-477F-A359-A40597F7270D}">
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2" s="10">
+        <v>2</v>
+      </c>
+      <c r="E2" s="10">
+        <v>30</v>
+      </c>
+      <c r="F2" s="10">
+        <v>15</v>
+      </c>
+      <c r="G2" s="10">
+        <v>0</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="I2" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D3" s="10">
+        <v>2</v>
+      </c>
+      <c r="E3" s="10">
+        <v>30</v>
+      </c>
+      <c r="F3" s="10">
+        <v>15</v>
+      </c>
+      <c r="G3" s="10">
+        <v>0</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="I3" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/assets/floor_2_data.xlsx
+++ b/assets/floor_2_data.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\M.Mead\9.FactoryView\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FECEA1C3-9BBC-41C5-B7E8-390A2A341868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB780C76-8EFD-43AC-8C9D-9F056736C520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="loc_name" sheetId="1" r:id="rId1"/>
     <sheet name="it_dev" sheetId="2" r:id="rId2"/>
     <sheet name="prod_comp" sheetId="9" r:id="rId3"/>
     <sheet name="machine" sheetId="8" r:id="rId4"/>
-    <sheet name="weight" sheetId="6" r:id="rId5"/>
-    <sheet name="zones" sheetId="5" r:id="rId6"/>
-    <sheet name="flow_pouch" sheetId="7" r:id="rId7"/>
-    <sheet name="flow_can" sheetId="10" r:id="rId8"/>
+    <sheet name="form_can_1" sheetId="12" r:id="rId5"/>
+    <sheet name="weight" sheetId="6" r:id="rId6"/>
+    <sheet name="zones" sheetId="5" r:id="rId7"/>
+    <sheet name="zones_noname" sheetId="13" r:id="rId8"/>
+    <sheet name="flow_powder" sheetId="11" r:id="rId9"/>
+    <sheet name="flow_pouch" sheetId="7" r:id="rId10"/>
+    <sheet name="flow_can" sheetId="10" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -84,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="283">
   <si>
     <t>Name</t>
   </si>
@@ -771,13 +774,175 @@
   </si>
   <si>
     <t>Gw-v-4</t>
+  </si>
+  <si>
+    <t>Document</t>
+  </si>
+  <si>
+    <t>Frequency</t>
+  </si>
+  <si>
+    <t>FormType</t>
+  </si>
+  <si>
+    <t>RecordedBy</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>DataSchema</t>
+  </si>
+  <si>
+    <t>Paper</t>
+  </si>
+  <si>
+    <t>Per production lot</t>
+  </si>
+  <si>
+    <t>Production</t>
+  </si>
+  <si>
+    <t>Product Code Settings (3)</t>
+  </si>
+  <si>
+    <t>Blender C</t>
+  </si>
+  <si>
+    <t>#eb6786</t>
+  </si>
+  <si>
+    <t>Raw Material Receiving Record</t>
+  </si>
+  <si>
+    <t>assets/docs/1000391098+5000006870_CAN/4.Dispensing/Process_P_126_128.pdf</t>
+  </si>
+  <si>
+    <t>White Area</t>
+  </si>
+  <si>
+    <t>assets/docs/1000391098+5000006870_CAN/5.Blender/Machine_P_046.pdf</t>
+  </si>
+  <si>
+    <t>Line Clearance Blending Area</t>
+  </si>
+  <si>
+    <t>assets/docs/1000391098+5000006870_CAN/5.Blender/Process_P_115.pdf</t>
+  </si>
+  <si>
+    <t>Verification of Weight Scale Record (1)</t>
+  </si>
+  <si>
+    <t>Verification of Weight Scale Record (2)</t>
+  </si>
+  <si>
+    <t>Verification of Weight Scale Record (3)</t>
+  </si>
+  <si>
+    <t>Vitamin#1</t>
+  </si>
+  <si>
+    <t>Vitamin#2</t>
+  </si>
+  <si>
+    <t>Vitamin#3</t>
+  </si>
+  <si>
+    <t>assets/docs/1000391098+5000006870_CAN/6.Vitamin%20Weighing/Machine_P_123.pdf</t>
+  </si>
+  <si>
+    <t>assets/docs/1000391098+5000006870_CAN/6.Vitamin%20Weighing/Machine_P_124.pdf</t>
+  </si>
+  <si>
+    <t>assets/docs/1000391098+5000006870_CAN/6.Vitamin%20Weighing/Machine_P_125.pdf</t>
+  </si>
+  <si>
+    <t>assets/docs/1000391098+5000006870_CAN/6.Vitamin%20Weighing/Process_P_120.pdf</t>
+  </si>
+  <si>
+    <t>Line Clarance &amp; Temp/ Humid Check (1)</t>
+  </si>
+  <si>
+    <t>Line Clarance &amp; Temp/ Humid Check (2)</t>
+  </si>
+  <si>
+    <t>Line Clarance &amp; Temp/ Humid Check (3)</t>
+  </si>
+  <si>
+    <t>assets/docs/1000391098+5000006870_CAN/6.Vitamin%20Weighing/Process_P_121.pdf</t>
+  </si>
+  <si>
+    <t>assets/docs/1000391098+5000006870_CAN/6.Vitamin%20Weighing/Process_P_122.pdf</t>
+  </si>
+  <si>
+    <t>assets/docs/1000391098+5000006870_CAN/5.Blender/Process_P_011.pdf</t>
+  </si>
+  <si>
+    <t>Tipping Record - Operator</t>
+  </si>
+  <si>
+    <t>assets/docs/1000391098+5000006870_CAN/5.Blender/Process_P_112.pdf</t>
+  </si>
+  <si>
+    <t>Product Changeover Command (4)</t>
+  </si>
+  <si>
+    <t>assets/docs/1000391098+5000006870_CAN/5.Blender/Process_P_142.pdf</t>
+  </si>
+  <si>
+    <t>#9ab6db</t>
+  </si>
+  <si>
+    <t>Sifter Screen Inspection Record (oPRP1)</t>
+  </si>
+  <si>
+    <t>Sifter</t>
+  </si>
+  <si>
+    <t>OEE Data Record Sheet - White Area</t>
+  </si>
+  <si>
+    <t>assets/docs/1000391098+5000006870_CAN/7.Sifter/Machine_P_006_009.pdf</t>
+  </si>
+  <si>
+    <t>Hoper and Sifter tightening Point Check</t>
+  </si>
+  <si>
+    <t>assets/docs/1000391098+5000006870_CAN/7.Sifter/Machine_P_049.pdf</t>
+  </si>
+  <si>
+    <t>Sifter Tailer Check Sheet</t>
+  </si>
+  <si>
+    <t>assets/docs/1000391098+5000006870_CAN/9.Can%20Filler/Machine_P_050.pdf</t>
+  </si>
+  <si>
+    <t>Mark</t>
+  </si>
+  <si>
+    <t>No.</t>
+  </si>
+  <si>
+    <t>0.Prestart</t>
+  </si>
+  <si>
+    <t>1.Re-config</t>
+  </si>
+  <si>
+    <t>continuous</t>
+  </si>
+  <si>
+    <t>machine</t>
+  </si>
+  <si>
+    <t>#fcbe03</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -794,6 +959,27 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0070C0"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="3" tint="0.39997558519241921"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="4"/>
       <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -852,7 +1038,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -870,6 +1056,18 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1290,6 +1488,306 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4FA26C3-CAFB-4728-933F-28CE0AA88343}">
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="16.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="112" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.44140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="7.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.88671875" style="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="D2" s="10">
+        <v>2</v>
+      </c>
+      <c r="E2" s="10">
+        <v>30</v>
+      </c>
+      <c r="F2" s="10">
+        <v>15</v>
+      </c>
+      <c r="G2" s="10">
+        <v>0</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="I2" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="D3" s="10">
+        <v>2</v>
+      </c>
+      <c r="E3" s="10">
+        <v>30</v>
+      </c>
+      <c r="F3" s="10">
+        <v>15</v>
+      </c>
+      <c r="G3" s="10">
+        <v>0</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="I3" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="D4" s="10">
+        <v>2</v>
+      </c>
+      <c r="E4" s="10">
+        <v>30</v>
+      </c>
+      <c r="F4" s="10">
+        <v>15</v>
+      </c>
+      <c r="G4" s="10">
+        <v>0</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="I4" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="D5" s="10">
+        <v>2</v>
+      </c>
+      <c r="E5" s="10">
+        <v>30</v>
+      </c>
+      <c r="F5" s="10">
+        <v>15</v>
+      </c>
+      <c r="G5" s="10">
+        <v>0</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="I5" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="D6" s="10">
+        <v>2</v>
+      </c>
+      <c r="E6" s="10">
+        <v>30</v>
+      </c>
+      <c r="F6" s="10">
+        <v>15</v>
+      </c>
+      <c r="G6" s="10">
+        <v>0</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="I6" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AC33B8A-E190-477F-A359-A40597F7270D}">
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2" s="10">
+        <v>2</v>
+      </c>
+      <c r="E2" s="10">
+        <v>30</v>
+      </c>
+      <c r="F2" s="10">
+        <v>15</v>
+      </c>
+      <c r="G2" s="10">
+        <v>0</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="I2" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D3" s="10">
+        <v>2</v>
+      </c>
+      <c r="E3" s="10">
+        <v>30</v>
+      </c>
+      <c r="F3" s="10">
+        <v>15</v>
+      </c>
+      <c r="G3" s="10">
+        <v>0</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="I3" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N25"/>
@@ -2683,6 +3181,531 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A82E3B6A-1D37-4BDB-B3B8-37A38B632E60}">
+  <dimension ref="A1:P16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="12"/>
+    <col min="2" max="2" width="38.77734375" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.109375" style="10" customWidth="1"/>
+    <col min="5" max="5" width="5" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.77734375" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.77734375" style="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="73.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9" style="10" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="50.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="63.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="8.88671875" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A1" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="P1" s="10" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="13">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="E2" s="11">
+        <v>626</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-950</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="13">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="E3" s="11">
+        <v>780</v>
+      </c>
+      <c r="F3" s="11">
+        <v>-630</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="13">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="E4" s="11">
+        <v>780</v>
+      </c>
+      <c r="F4" s="11">
+        <v>-600</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="L4" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="N4" s="11" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="13">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="E5" s="11">
+        <v>780</v>
+      </c>
+      <c r="F5" s="11">
+        <v>-570</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="13">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="E6" s="11">
+        <v>780</v>
+      </c>
+      <c r="F6" s="11">
+        <v>-540</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="13">
+        <v>6</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="E7" s="11">
+        <v>1240</v>
+      </c>
+      <c r="F7" s="11">
+        <v>-574</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="13">
+        <v>7</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="E8" s="11">
+        <v>892</v>
+      </c>
+      <c r="F8" s="11">
+        <v>-855</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="13">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="E9" s="11">
+        <v>1126</v>
+      </c>
+      <c r="F9" s="11">
+        <v>-855</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="13">
+        <v>9</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="E10" s="11">
+        <v>1291</v>
+      </c>
+      <c r="F10" s="11">
+        <v>-855</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="13">
+        <v>10</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="E11" s="11">
+        <v>892</v>
+      </c>
+      <c r="F11" s="11">
+        <v>-820</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="13">
+        <v>11</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="E12" s="11">
+        <v>1126</v>
+      </c>
+      <c r="F12" s="11">
+        <v>-820</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="E13" s="11">
+        <v>1291</v>
+      </c>
+      <c r="F13" s="11">
+        <v>-820</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="13">
+        <v>13</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="E14" s="11">
+        <v>1210</v>
+      </c>
+      <c r="F14" s="11">
+        <v>-190</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>281</v>
+      </c>
+      <c r="E15" s="16">
+        <v>1210</v>
+      </c>
+      <c r="F15" s="16">
+        <v>-160</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>269</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="15">
+        <v>15</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>274</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="E16" s="16">
+        <v>1210</v>
+      </c>
+      <c r="F16" s="16">
+        <v>-130</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>269</v>
+      </c>
+      <c r="J16" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>275</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A113FB90-F9A2-4A63-A07C-A429C0E9DE7B}">
   <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -2863,7 +3886,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -3310,9 +4333,425 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4FA26C3-CAFB-4728-933F-28CE0AA88343}">
-  <dimension ref="A1:J15"/>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BE13484-8EF2-4DFC-A1DA-64C2CD377CCC}">
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15.21875" style="10" customWidth="1"/>
+    <col min="2" max="8" width="8.88671875" style="10"/>
+    <col min="9" max="9" width="18" style="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B2" s="10">
+        <v>-1771</v>
+      </c>
+      <c r="C2" s="10">
+        <v>-218</v>
+      </c>
+      <c r="D2" s="10">
+        <v>-1175</v>
+      </c>
+      <c r="E2" s="10">
+        <v>-24</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="G2" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="H2" s="10">
+        <v>14</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B3" s="10">
+        <v>-1771</v>
+      </c>
+      <c r="C3" s="10">
+        <v>-24</v>
+      </c>
+      <c r="D3" s="10">
+        <v>-1095</v>
+      </c>
+      <c r="E3" s="10">
+        <v>717</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="G3" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="H3" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B4" s="10">
+        <v>-1095</v>
+      </c>
+      <c r="C4" s="10">
+        <v>295</v>
+      </c>
+      <c r="D4" s="10">
+        <v>-973</v>
+      </c>
+      <c r="E4" s="10">
+        <v>609</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="G4" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="H4" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B5" s="10">
+        <v>-893</v>
+      </c>
+      <c r="C5" s="10">
+        <v>-162</v>
+      </c>
+      <c r="D5" s="10">
+        <v>-469</v>
+      </c>
+      <c r="E5" s="10">
+        <v>401</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="G5" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="H5" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B6" s="10">
+        <v>-1280</v>
+      </c>
+      <c r="C6" s="10">
+        <v>-1319</v>
+      </c>
+      <c r="D6" s="10">
+        <v>-540</v>
+      </c>
+      <c r="E6" s="10">
+        <v>-1183</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="G6" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="H6" s="10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B7" s="10">
+        <v>734</v>
+      </c>
+      <c r="C7" s="10">
+        <v>-793</v>
+      </c>
+      <c r="D7" s="10">
+        <v>1527</v>
+      </c>
+      <c r="E7" s="10">
+        <v>-25</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="G7" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="H7" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B8" s="10">
+        <v>545</v>
+      </c>
+      <c r="C8" s="10">
+        <v>-598</v>
+      </c>
+      <c r="D8" s="10">
+        <v>734</v>
+      </c>
+      <c r="E8" s="10">
+        <v>-371</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="G8" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="H8" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B9" s="10">
+        <v>734</v>
+      </c>
+      <c r="C9" s="10">
+        <v>-956</v>
+      </c>
+      <c r="D9" s="10">
+        <v>1331</v>
+      </c>
+      <c r="E9" s="10">
+        <v>-796</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="G9" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="H9" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B10" s="10">
+        <v>1233</v>
+      </c>
+      <c r="C10" s="10">
+        <v>-1068</v>
+      </c>
+      <c r="D10" s="10">
+        <v>1395</v>
+      </c>
+      <c r="E10" s="10">
+        <v>-956</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="G10" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="H10" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B11" s="10">
+        <v>461</v>
+      </c>
+      <c r="C11" s="10">
+        <v>-1182</v>
+      </c>
+      <c r="D11" s="10">
+        <v>734</v>
+      </c>
+      <c r="E11" s="10">
+        <v>-711</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="G11" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="H11" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B12" s="10">
+        <v>2133</v>
+      </c>
+      <c r="C12" s="10">
+        <v>-1311</v>
+      </c>
+      <c r="D12" s="10">
+        <v>2655</v>
+      </c>
+      <c r="E12" s="10">
+        <v>186</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="G12" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="H12" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B13" s="10">
+        <v>-1772</v>
+      </c>
+      <c r="C13" s="10">
+        <v>-1183</v>
+      </c>
+      <c r="D13" s="10">
+        <v>-540</v>
+      </c>
+      <c r="E13" s="10">
+        <v>-218</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="G13" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="H13" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B14" s="10">
+        <v>-464</v>
+      </c>
+      <c r="C14" s="10">
+        <v>-1183</v>
+      </c>
+      <c r="D14" s="10">
+        <v>461</v>
+      </c>
+      <c r="E14" s="10">
+        <v>-218</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="G14" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="H14" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B15" s="10">
+        <v>1527</v>
+      </c>
+      <c r="C15" s="10">
+        <v>-1187</v>
+      </c>
+      <c r="D15" s="10">
+        <v>1924</v>
+      </c>
+      <c r="E15" s="10">
+        <v>-982</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="G15" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="H15" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B16" s="10">
+        <v>1527</v>
+      </c>
+      <c r="C16" s="10">
+        <v>-982</v>
+      </c>
+      <c r="D16" s="10">
+        <v>2126</v>
+      </c>
+      <c r="E16" s="10">
+        <v>-6</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="G16" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="H16" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B17" s="10">
+        <v>-2694</v>
+      </c>
+      <c r="C17" s="10">
+        <v>-603</v>
+      </c>
+      <c r="D17" s="10">
+        <v>-1773</v>
+      </c>
+      <c r="E17" s="10">
+        <v>1304</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="G17" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="H17" s="10">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57EE0D85-DD60-4891-B20F-895CEC338B14}">
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.21875" style="10" bestFit="1" customWidth="1"/>
@@ -3488,28 +4927,28 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
-        <v>172</v>
+        <v>196</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>180</v>
+        <v>206</v>
       </c>
       <c r="D6" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" s="10">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F6" s="10">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G6" s="10">
         <v>0</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>164</v>
+        <v>197</v>
       </c>
       <c r="I6" s="10" t="b">
         <v>1</v>
@@ -3517,28 +4956,28 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>180</v>
+        <v>207</v>
       </c>
       <c r="D7" s="10">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="E7" s="10">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F7" s="10">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G7" s="10">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>164</v>
+        <v>197</v>
       </c>
       <c r="I7" s="10" t="b">
         <v>1</v>
@@ -3546,28 +4985,28 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
-        <v>174</v>
+        <v>200</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>180</v>
+        <v>208</v>
       </c>
       <c r="D8" s="10">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="E8" s="10">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F8" s="10">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G8" s="10">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>164</v>
+        <v>197</v>
       </c>
       <c r="I8" s="10" t="b">
         <v>1</v>
@@ -3575,28 +5014,28 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>180</v>
+        <v>209</v>
       </c>
       <c r="D9" s="10">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="E9" s="10">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F9" s="10">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G9" s="10">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>164</v>
+        <v>197</v>
       </c>
       <c r="I9" s="10" t="b">
         <v>1</v>
@@ -3604,281 +5043,34 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="D10" s="10">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="E10" s="10">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F10" s="10">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G10" s="10">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>164</v>
+        <v>197</v>
       </c>
       <c r="I10" s="10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="D11" s="10">
-        <v>1</v>
-      </c>
-      <c r="E11" s="10">
-        <v>20</v>
-      </c>
-      <c r="F11" s="10">
-        <v>5</v>
-      </c>
-      <c r="G11" s="10">
-        <v>0</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="I11" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A12" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="D12" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="E12" s="10">
-        <v>20</v>
-      </c>
-      <c r="F12" s="10">
-        <v>5</v>
-      </c>
-      <c r="G12" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="I12" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A13" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="D13" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="E13" s="10">
-        <v>20</v>
-      </c>
-      <c r="F13" s="10">
-        <v>5</v>
-      </c>
-      <c r="G13" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="I13" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A14" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="D14" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="E14" s="10">
-        <v>20</v>
-      </c>
-      <c r="F14" s="10">
-        <v>5</v>
-      </c>
-      <c r="G14" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="I14" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A15" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="D15" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="E15" s="10">
-        <v>20</v>
-      </c>
-      <c r="F15" s="10">
-        <v>5</v>
-      </c>
-      <c r="G15" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="I15" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AC33B8A-E190-477F-A359-A40597F7270D}">
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="J1" s="10" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="D2" s="10">
-        <v>2</v>
-      </c>
-      <c r="E2" s="10">
-        <v>30</v>
-      </c>
-      <c r="F2" s="10">
-        <v>15</v>
-      </c>
-      <c r="G2" s="10">
-        <v>0</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="I2" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="D3" s="10">
-        <v>2</v>
-      </c>
-      <c r="E3" s="10">
-        <v>30</v>
-      </c>
-      <c r="F3" s="10">
-        <v>15</v>
-      </c>
-      <c r="G3" s="10">
-        <v>0</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="I3" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
-</worksheet>
 </file>
--- a/assets/floor_2_data.xlsx
+++ b/assets/floor_2_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\M.Mead\9.FactoryView\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB780C76-8EFD-43AC-8C9D-9F056736C520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94138BE5-3657-4AA8-96E8-166F2D8326CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="loc_name" sheetId="1" r:id="rId1"/>
@@ -18,12 +18,13 @@
     <sheet name="prod_comp" sheetId="9" r:id="rId3"/>
     <sheet name="machine" sheetId="8" r:id="rId4"/>
     <sheet name="form_can_1" sheetId="12" r:id="rId5"/>
-    <sheet name="weight" sheetId="6" r:id="rId6"/>
-    <sheet name="zones" sheetId="5" r:id="rId7"/>
-    <sheet name="zones_noname" sheetId="13" r:id="rId8"/>
-    <sheet name="flow_powder" sheetId="11" r:id="rId9"/>
-    <sheet name="flow_pouch" sheetId="7" r:id="rId10"/>
-    <sheet name="flow_can" sheetId="10" r:id="rId11"/>
+    <sheet name="form_pouch_1" sheetId="14" r:id="rId6"/>
+    <sheet name="weight" sheetId="6" r:id="rId7"/>
+    <sheet name="zones" sheetId="5" r:id="rId8"/>
+    <sheet name="zones_noname" sheetId="13" r:id="rId9"/>
+    <sheet name="flow_powder" sheetId="11" r:id="rId10"/>
+    <sheet name="flow_pouch" sheetId="7" r:id="rId11"/>
+    <sheet name="flow_can" sheetId="10" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -87,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="295">
   <si>
     <t>Name</t>
   </si>
@@ -878,9 +879,6 @@
     <t>assets/docs/1000391098+5000006870_CAN/5.Blender/Process_P_011.pdf</t>
   </si>
   <si>
-    <t>Tipping Record - Operator</t>
-  </si>
-  <si>
     <t>assets/docs/1000391098+5000006870_CAN/5.Blender/Process_P_112.pdf</t>
   </si>
   <si>
@@ -936,6 +934,45 @@
   </si>
   <si>
     <t>#fcbe03</t>
+  </si>
+  <si>
+    <t>assets/docs/1000381996+1000381979_POUCH/4.Dispensing/Process_P_108.pdf</t>
+  </si>
+  <si>
+    <t>assets/docs/1000381996+1000381979_POUCH/5.Blender/Process_P_097.pdf</t>
+  </si>
+  <si>
+    <t>assets/docs/1000381996+1000381979_POUCH/5.Blender/Process_P_119.pdf</t>
+  </si>
+  <si>
+    <t>assets/docs/1000381996+1000381979_POUCH/5.Blender/Process_P_013.pdf</t>
+  </si>
+  <si>
+    <t>assets/docs/1000381996+1000381979_POUCH/5.Blender/Process_P_095.pdf</t>
+  </si>
+  <si>
+    <t>assets/docs/1000381996+1000381979_POUCH/5.Blender/Machine_P_043_044.pdf</t>
+  </si>
+  <si>
+    <t>Tipping Record (CCP1)</t>
+  </si>
+  <si>
+    <t>assets/docs/1000381996+1000381979_POUCH/6.Vitamin%20Weighing/Machine_P_103.pdf</t>
+  </si>
+  <si>
+    <t>assets/docs/1000381996+1000381979_POUCH/6.Vitamin%20Weighing/Machine_P_104.pdf</t>
+  </si>
+  <si>
+    <t>assets/docs/1000381996+1000381979_POUCH/6.Vitamin%20Weighing/Process_P_101.pdf</t>
+  </si>
+  <si>
+    <t>assets/docs/1000381996+1000381979_POUCH/6.Vitamin%20Weighing/Process_P_102.pdf</t>
+  </si>
+  <si>
+    <t>assets/docs/1000381996+1000381979_POUCH/7.Sifter/Machine_P_006_007.pdf</t>
+  </si>
+  <si>
+    <t>assets/docs/1000381996+1000381979_POUCH/7.Sifter/Machine_P_045.pdf</t>
   </si>
 </sst>
 </file>
@@ -1038,7 +1075,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1068,6 +1105,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1489,6 +1527,332 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57EE0D85-DD60-4891-B20F-895CEC338B14}">
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="16.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="112" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.44140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="7.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.88671875" style="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="D2" s="10">
+        <v>2</v>
+      </c>
+      <c r="E2" s="10">
+        <v>30</v>
+      </c>
+      <c r="F2" s="10">
+        <v>15</v>
+      </c>
+      <c r="G2" s="10">
+        <v>0</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="I2" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="D3" s="10">
+        <v>2</v>
+      </c>
+      <c r="E3" s="10">
+        <v>30</v>
+      </c>
+      <c r="F3" s="10">
+        <v>15</v>
+      </c>
+      <c r="G3" s="10">
+        <v>0</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="I3" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="D4" s="10">
+        <v>2</v>
+      </c>
+      <c r="E4" s="10">
+        <v>30</v>
+      </c>
+      <c r="F4" s="10">
+        <v>15</v>
+      </c>
+      <c r="G4" s="10">
+        <v>0</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="I4" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="D5" s="10">
+        <v>2</v>
+      </c>
+      <c r="E5" s="10">
+        <v>30</v>
+      </c>
+      <c r="F5" s="10">
+        <v>15</v>
+      </c>
+      <c r="G5" s="10">
+        <v>0</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="I5" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="D6" s="10">
+        <v>1</v>
+      </c>
+      <c r="E6" s="10">
+        <v>20</v>
+      </c>
+      <c r="F6" s="10">
+        <v>5</v>
+      </c>
+      <c r="G6" s="10">
+        <v>0</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="I6" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="D7" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="E7" s="10">
+        <v>20</v>
+      </c>
+      <c r="F7" s="10">
+        <v>5</v>
+      </c>
+      <c r="G7" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="I7" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="D8" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="E8" s="10">
+        <v>20</v>
+      </c>
+      <c r="F8" s="10">
+        <v>5</v>
+      </c>
+      <c r="G8" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="I8" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="D9" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="E9" s="10">
+        <v>20</v>
+      </c>
+      <c r="F9" s="10">
+        <v>5</v>
+      </c>
+      <c r="G9" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="I9" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="D10" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="E10" s="10">
+        <v>20</v>
+      </c>
+      <c r="F10" s="10">
+        <v>5</v>
+      </c>
+      <c r="G10" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="I10" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4FA26C3-CAFB-4728-933F-28CE0AA88343}">
   <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -1687,7 +2051,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AC33B8A-E190-477F-A359-A40597F7270D}">
   <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -3206,7 +3570,7 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>0</v>
@@ -3215,7 +3579,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E1" s="10" t="s">
         <v>2</v>
@@ -3265,7 +3629,7 @@
         <v>235</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E2" s="11">
         <v>626</v>
@@ -3294,7 +3658,7 @@
         <v>235</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E3" s="11">
         <v>780</v>
@@ -3317,13 +3681,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>235</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E4" s="11">
         <v>780</v>
@@ -3361,7 +3725,7 @@
         <v>235</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E5" s="11">
         <v>780</v>
@@ -3376,7 +3740,7 @@
         <v>240</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -3384,13 +3748,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>263</v>
+        <v>288</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>235</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E6" s="11">
         <v>780</v>
@@ -3402,10 +3766,10 @@
         <v>239</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="7" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -3413,25 +3777,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>235</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E7" s="11">
         <v>1240</v>
       </c>
       <c r="F7" s="11">
-        <v>-574</v>
+        <v>-570</v>
       </c>
       <c r="G7" s="11" t="s">
         <v>243</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="K7" s="11" t="s">
         <v>244</v>
@@ -3439,176 +3803,176 @@
     </row>
     <row r="8" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>235</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>281</v>
-      </c>
-      <c r="E8" s="11">
+        <v>280</v>
+      </c>
+      <c r="E8" s="17">
         <v>892</v>
       </c>
       <c r="F8" s="11">
         <v>-855</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
     </row>
     <row r="9" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>235</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>281</v>
-      </c>
-      <c r="E9" s="11">
+        <v>280</v>
+      </c>
+      <c r="E9" s="17">
         <v>1126</v>
       </c>
       <c r="F9" s="11">
         <v>-855</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>235</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>281</v>
-      </c>
-      <c r="E10" s="11">
+        <v>280</v>
+      </c>
+      <c r="E10" s="17">
         <v>1291</v>
       </c>
       <c r="F10" s="11">
         <v>-855</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="13">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>235</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>281</v>
-      </c>
-      <c r="E11" s="11">
+        <v>280</v>
+      </c>
+      <c r="E11" s="17">
         <v>892</v>
       </c>
       <c r="F11" s="11">
         <v>-820</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="13">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>235</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>281</v>
-      </c>
-      <c r="E12" s="11">
+        <v>280</v>
+      </c>
+      <c r="E12" s="17">
         <v>1126</v>
       </c>
       <c r="F12" s="11">
         <v>-820</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="13" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="13">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>235</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>281</v>
-      </c>
-      <c r="E13" s="11">
+        <v>280</v>
+      </c>
+      <c r="E13" s="17">
         <v>1291</v>
       </c>
       <c r="F13" s="11">
         <v>-820</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="14" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -3616,13 +3980,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>235</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E14" s="11">
         <v>1210</v>
@@ -3631,13 +3995,13 @@
         <v>-190</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="15" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.2">
@@ -3645,13 +4009,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C15" s="16" t="s">
         <v>235</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E15" s="16">
         <v>1210</v>
@@ -3660,13 +4024,13 @@
         <v>-160</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="16" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.2">
@@ -3674,13 +4038,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C16" s="16" t="s">
         <v>235</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E16" s="16">
         <v>1210</v>
@@ -3689,13 +4053,13 @@
         <v>-130</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="J16" s="16" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
   </sheetData>
@@ -3706,6 +4070,443 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FB71D57-BE2D-4E53-8949-88C80A2C6281}">
+  <dimension ref="A1:P13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="12"/>
+    <col min="2" max="2" width="38.77734375" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.109375" style="10" customWidth="1"/>
+    <col min="5" max="5" width="5" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.77734375" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.77734375" style="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="76" style="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9" style="10" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="50.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="63.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="8.88671875" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A1" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="P1" s="10" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="13">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="E2" s="11">
+        <v>626</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-950</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="13">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="E3" s="11">
+        <v>950</v>
+      </c>
+      <c r="F3" s="11">
+        <v>-630</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="13">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="E4" s="11">
+        <v>950</v>
+      </c>
+      <c r="F4" s="11">
+        <v>-600</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="L4" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="N4" s="11" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="13">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="E5" s="11">
+        <v>950</v>
+      </c>
+      <c r="F5" s="11">
+        <v>-570</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="13">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="E6" s="11">
+        <v>950</v>
+      </c>
+      <c r="F6" s="11">
+        <v>-540</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="13">
+        <v>6</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="E7" s="11">
+        <v>1240</v>
+      </c>
+      <c r="F7" s="11">
+        <v>-540</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="13">
+        <v>8</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="E8" s="11">
+        <v>1291</v>
+      </c>
+      <c r="F8" s="11">
+        <v>-855</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="13">
+        <v>9</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="E9" s="11">
+        <v>892</v>
+      </c>
+      <c r="F9" s="11">
+        <v>-855</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="13">
+        <v>11</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="E10" s="11">
+        <v>1291</v>
+      </c>
+      <c r="F10" s="11">
+        <v>-820</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="13">
+        <v>12</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="E11" s="11">
+        <v>892</v>
+      </c>
+      <c r="F11" s="11">
+        <v>-820</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="13">
+        <v>13</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="E12" s="11">
+        <v>1330</v>
+      </c>
+      <c r="F12" s="11">
+        <v>-430</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="15">
+        <v>14</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>273</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>279</v>
+      </c>
+      <c r="E13" s="16">
+        <v>1330</v>
+      </c>
+      <c r="F13" s="16">
+        <v>-400</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>268</v>
+      </c>
+      <c r="J13" s="16" t="s">
+        <v>281</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>294</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A113FB90-F9A2-4A63-A07C-A429C0E9DE7B}">
   <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -3886,7 +4687,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -4333,7 +5134,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BE13484-8EF2-4DFC-A1DA-64C2CD377CCC}">
   <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -4747,330 +5548,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57EE0D85-DD60-4891-B20F-895CEC338B14}">
-  <dimension ref="A1:J10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="16.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="112" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.44140625" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.77734375" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="7.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.88671875" style="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.5546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="J1" s="10" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="D2" s="10">
-        <v>2</v>
-      </c>
-      <c r="E2" s="10">
-        <v>30</v>
-      </c>
-      <c r="F2" s="10">
-        <v>15</v>
-      </c>
-      <c r="G2" s="10">
-        <v>0</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="I2" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J2" s="10" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="D3" s="10">
-        <v>2</v>
-      </c>
-      <c r="E3" s="10">
-        <v>30</v>
-      </c>
-      <c r="F3" s="10">
-        <v>15</v>
-      </c>
-      <c r="G3" s="10">
-        <v>0</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="I3" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J3" s="10" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="D4" s="10">
-        <v>2</v>
-      </c>
-      <c r="E4" s="10">
-        <v>30</v>
-      </c>
-      <c r="F4" s="10">
-        <v>15</v>
-      </c>
-      <c r="G4" s="10">
-        <v>0</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="I4" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="D5" s="10">
-        <v>2</v>
-      </c>
-      <c r="E5" s="10">
-        <v>30</v>
-      </c>
-      <c r="F5" s="10">
-        <v>15</v>
-      </c>
-      <c r="G5" s="10">
-        <v>0</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="I5" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J5" s="10" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="D6" s="10">
-        <v>1</v>
-      </c>
-      <c r="E6" s="10">
-        <v>20</v>
-      </c>
-      <c r="F6" s="10">
-        <v>5</v>
-      </c>
-      <c r="G6" s="10">
-        <v>0</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="I6" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="D7" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="E7" s="10">
-        <v>20</v>
-      </c>
-      <c r="F7" s="10">
-        <v>5</v>
-      </c>
-      <c r="G7" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="I7" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="D8" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="E8" s="10">
-        <v>20</v>
-      </c>
-      <c r="F8" s="10">
-        <v>5</v>
-      </c>
-      <c r="G8" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="I8" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="D9" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="E9" s="10">
-        <v>20</v>
-      </c>
-      <c r="F9" s="10">
-        <v>5</v>
-      </c>
-      <c r="G9" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="I9" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="D10" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="E10" s="10">
-        <v>20</v>
-      </c>
-      <c r="F10" s="10">
-        <v>5</v>
-      </c>
-      <c r="G10" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="I10" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/assets/floor_2_data.xlsx
+++ b/assets/floor_2_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\M.Mead\9.FactoryView\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94138BE5-3657-4AA8-96E8-166F2D8326CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8724E58-E074-42AC-A3FB-28B639165B20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="loc_name" sheetId="1" r:id="rId1"/>
@@ -22,9 +22,10 @@
     <sheet name="weight" sheetId="6" r:id="rId7"/>
     <sheet name="zones" sheetId="5" r:id="rId8"/>
     <sheet name="zones_noname" sheetId="13" r:id="rId9"/>
-    <sheet name="flow_powder" sheetId="11" r:id="rId10"/>
-    <sheet name="flow_pouch" sheetId="7" r:id="rId11"/>
-    <sheet name="flow_can" sheetId="10" r:id="rId12"/>
+    <sheet name="building" sheetId="15" r:id="rId10"/>
+    <sheet name="flow_powder" sheetId="11" r:id="rId11"/>
+    <sheet name="flow_pouch" sheetId="7" r:id="rId12"/>
+    <sheet name="flow_can" sheetId="10" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -88,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="300">
   <si>
     <t>Name</t>
   </si>
@@ -973,6 +974,21 @@
   </si>
   <si>
     <t>assets/docs/1000381996+1000381979_POUCH/7.Sifter/Machine_P_045.pdf</t>
+  </si>
+  <si>
+    <t>#55ab46</t>
+  </si>
+  <si>
+    <t>#071cdb</t>
+  </si>
+  <si>
+    <t>RTD f2</t>
+  </si>
+  <si>
+    <t>Enfa f2</t>
+  </si>
+  <si>
+    <t>Alacta f2</t>
   </si>
 </sst>
 </file>
@@ -1527,6 +1543,176 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59F60705-402B-438D-B19F-19DE294CC7AB}">
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="21.44140625" style="10" customWidth="1"/>
+    <col min="2" max="7" width="8.88671875" style="10"/>
+    <col min="8" max="8" width="7.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.77734375" style="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="B2" s="10">
+        <v>-2703</v>
+      </c>
+      <c r="C2" s="10">
+        <v>-584</v>
+      </c>
+      <c r="D2" s="10">
+        <v>-1785</v>
+      </c>
+      <c r="E2" s="10">
+        <v>1308</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="G2" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="H2" s="10">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="B3" s="10">
+        <v>-1782</v>
+      </c>
+      <c r="C3" s="10">
+        <v>-194</v>
+      </c>
+      <c r="D3" s="10">
+        <v>-471</v>
+      </c>
+      <c r="E3" s="10">
+        <v>930</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="G3" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="H3" s="10">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="B4" s="10">
+        <v>-1782</v>
+      </c>
+      <c r="C4" s="10">
+        <v>-1300</v>
+      </c>
+      <c r="D4" s="10">
+        <v>2645</v>
+      </c>
+      <c r="E4" s="10">
+        <v>-194</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="G4" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="H4" s="10">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B5" s="10">
+        <v>-471</v>
+      </c>
+      <c r="C5" s="10">
+        <v>-194</v>
+      </c>
+      <c r="D5" s="10">
+        <v>880</v>
+      </c>
+      <c r="E5" s="10">
+        <v>733</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="G5" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="H5" s="10">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B6" s="10">
+        <v>880</v>
+      </c>
+      <c r="C6" s="10">
+        <v>-194</v>
+      </c>
+      <c r="D6" s="10">
+        <v>2644</v>
+      </c>
+      <c r="E6" s="10">
+        <v>198</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="G6" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="H6" s="10">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57EE0D85-DD60-4891-B20F-895CEC338B14}">
   <dimension ref="A1:J10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -1852,7 +2038,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4FA26C3-CAFB-4728-933F-28CE0AA88343}">
   <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -2051,7 +2237,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AC33B8A-E190-477F-A359-A40597F7270D}">
   <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>

--- a/assets/floor_2_data.xlsx
+++ b/assets/floor_2_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\M.Mead\9.FactoryView\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8724E58-E074-42AC-A3FB-28B639165B20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC01EED5-689C-4A6A-AFBA-FB3CD182DBD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="loc_name" sheetId="1" r:id="rId1"/>
@@ -89,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="305">
   <si>
     <t>Name</t>
   </si>
@@ -989,6 +989,21 @@
   </si>
   <si>
     <t>Alacta f2</t>
+  </si>
+  <si>
+    <t>assets/docs/1000381996+1000381979_POUCH/0.Overall/P_080_092.pdf</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>Manufacturing Batch Record</t>
+  </si>
+  <si>
+    <t>Photo</t>
+  </si>
+  <si>
+    <t>https://x2t0cwasywcrqeuc.private.blob.vercel-storage.com/machines/Blender.png</t>
   </si>
 </sst>
 </file>
@@ -1091,7 +1106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1122,6 +1137,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3526,7 +3544,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9DA2CD0-4EB4-4612-8E4D-C2326FA17524}">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.5546875" style="10" bestFit="1" customWidth="1"/>
@@ -3534,10 +3552,12 @@
     <col min="5" max="5" width="15.109375" style="10" customWidth="1"/>
     <col min="6" max="6" width="8.88671875" style="10"/>
     <col min="7" max="7" width="12.44140625" style="10" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="10"/>
+    <col min="8" max="8" width="8.88671875" style="10"/>
+    <col min="9" max="9" width="66.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -3562,8 +3582,11 @@
       <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I1" s="12" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
         <v>190</v>
       </c>
@@ -3585,8 +3608,11 @@
       <c r="G2" s="10" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I2" s="10" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
         <v>191</v>
       </c>
@@ -3608,8 +3634,11 @@
       <c r="G3" s="10" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I3" s="10" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
         <v>192</v>
       </c>
@@ -3631,8 +3660,11 @@
       <c r="G4" s="10" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I4" s="10" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>193</v>
       </c>
@@ -3654,8 +3686,11 @@
       <c r="G5" s="10" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I5" s="10" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>147</v>
       </c>
@@ -3669,7 +3704,7 @@
         <v>-706</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>148</v>
       </c>
@@ -3683,7 +3718,7 @@
         <v>-572</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>149</v>
       </c>
@@ -3697,7 +3732,7 @@
         <v>-417</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
         <v>150</v>
       </c>
@@ -3711,7 +3746,7 @@
         <v>-305</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>146</v>
       </c>
@@ -4257,7 +4292,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FB71D57-BE2D-4E53-8949-88C80A2C6281}">
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="12"/>
@@ -4329,70 +4364,70 @@
         <v>234</v>
       </c>
     </row>
-    <row r="2" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="13">
+    <row r="2" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="18">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="C2" s="11" t="s">
+      <c r="B2" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="C2" s="14" t="s">
         <v>235</v>
       </c>
       <c r="D2" s="14" t="s">
         <v>277</v>
       </c>
-      <c r="E2" s="11">
+      <c r="E2" s="14">
         <v>626</v>
       </c>
-      <c r="F2" s="11">
-        <v>-950</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="J2" s="11" t="s">
+      <c r="F2" s="14">
+        <v>-980</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="J2" s="14" t="s">
         <v>240</v>
       </c>
-      <c r="K2" s="11" t="s">
-        <v>282</v>
+      <c r="K2" s="14" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="3" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C3" s="11" t="s">
         <v>235</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E3" s="11">
-        <v>950</v>
+        <v>626</v>
       </c>
       <c r="F3" s="11">
-        <v>-630</v>
+        <v>-950</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>239</v>
+        <v>133</v>
       </c>
       <c r="J3" s="11" t="s">
         <v>240</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>264</v>
+        <v>245</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>235</v>
@@ -4404,7 +4439,7 @@
         <v>950</v>
       </c>
       <c r="F4" s="11">
-        <v>-600</v>
+        <v>-630</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>239</v>
@@ -4413,24 +4448,15 @@
         <v>240</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>285</v>
-      </c>
-      <c r="L4" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="M4" s="11" t="s">
-        <v>237</v>
-      </c>
-      <c r="N4" s="11" t="s">
-        <v>237</v>
+        <v>283</v>
       </c>
     </row>
     <row r="5" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>238</v>
+        <v>264</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>235</v>
@@ -4442,7 +4468,7 @@
         <v>950</v>
       </c>
       <c r="F5" s="11">
-        <v>-570</v>
+        <v>-600</v>
       </c>
       <c r="G5" s="11" t="s">
         <v>239</v>
@@ -4451,73 +4477,82 @@
         <v>240</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>284</v>
+        <v>285</v>
+      </c>
+      <c r="L5" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="N5" s="11" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="6" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>288</v>
+        <v>238</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>235</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E6" s="11">
         <v>950</v>
       </c>
       <c r="F6" s="11">
-        <v>-540</v>
+        <v>-570</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="J6" s="14" t="s">
-        <v>281</v>
+      <c r="J6" s="11" t="s">
+        <v>240</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>269</v>
+        <v>288</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="D7" s="11" t="s">
-        <v>280</v>
+      <c r="D7" s="14" t="s">
+        <v>279</v>
       </c>
       <c r="E7" s="11">
-        <v>1240</v>
+        <v>950</v>
       </c>
       <c r="F7" s="11">
         <v>-540</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="J7" s="11" t="s">
-        <v>266</v>
+        <v>239</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>281</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="8" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="13">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>235</v>
@@ -4526,27 +4561,27 @@
         <v>280</v>
       </c>
       <c r="E8" s="11">
-        <v>1291</v>
+        <v>1240</v>
       </c>
       <c r="F8" s="11">
-        <v>-855</v>
+        <v>-540</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="J8" s="11" t="s">
         <v>266</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="9" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>235</v>
@@ -4555,27 +4590,27 @@
         <v>280</v>
       </c>
       <c r="E9" s="11">
-        <v>892</v>
+        <v>1291</v>
       </c>
       <c r="F9" s="11">
         <v>-855</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J9" s="11" t="s">
         <v>266</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="13">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>235</v>
@@ -4584,27 +4619,27 @@
         <v>280</v>
       </c>
       <c r="E10" s="11">
-        <v>1291</v>
+        <v>892</v>
       </c>
       <c r="F10" s="11">
-        <v>-820</v>
+        <v>-855</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J10" s="11" t="s">
         <v>266</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="11" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="13">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>235</v>
@@ -4613,27 +4648,27 @@
         <v>280</v>
       </c>
       <c r="E11" s="11">
-        <v>892</v>
+        <v>1291</v>
       </c>
       <c r="F11" s="11">
         <v>-820</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J11" s="11" t="s">
         <v>266</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="12" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="13">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>235</v>
@@ -4642,47 +4677,76 @@
         <v>280</v>
       </c>
       <c r="E12" s="11">
-        <v>1330</v>
+        <v>892</v>
       </c>
       <c r="F12" s="11">
-        <v>-430</v>
+        <v>-820</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="J12" s="11" t="s">
         <v>266</v>
       </c>
       <c r="K12" s="11" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="13">
+        <v>13</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="E13" s="11">
+        <v>1330</v>
+      </c>
+      <c r="F13" s="11">
+        <v>-430</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="K13" s="11" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="13" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="15">
+    <row r="14" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="15">
         <v>14</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B14" s="16" t="s">
         <v>273</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C14" s="16" t="s">
         <v>235</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D14" s="16" t="s">
         <v>279</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E14" s="16">
         <v>1330</v>
       </c>
-      <c r="F13" s="16">
+      <c r="F14" s="16">
         <v>-400</v>
       </c>
-      <c r="G13" s="16" t="s">
+      <c r="G14" s="16" t="s">
         <v>268</v>
       </c>
-      <c r="J13" s="16" t="s">
+      <c r="J14" s="16" t="s">
         <v>281</v>
       </c>
-      <c r="K13" s="16" t="s">
+      <c r="K14" s="16" t="s">
         <v>294</v>
       </c>
     </row>

--- a/assets/floor_2_data.xlsx
+++ b/assets/floor_2_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\M.Mead\9.FactoryView\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC01EED5-689C-4A6A-AFBA-FB3CD182DBD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A42F92F-0B07-48B5-91B1-9590D928F7BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="loc_name" sheetId="1" r:id="rId1"/>
@@ -89,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="313">
   <si>
     <t>Name</t>
   </si>
@@ -1004,6 +1004,30 @@
   </si>
   <si>
     <t>https://x2t0cwasywcrqeuc.private.blob.vercel-storage.com/machines/Blender.png</t>
+  </si>
+  <si>
+    <t>Preblend</t>
+  </si>
+  <si>
+    <t>Capacity</t>
+  </si>
+  <si>
+    <t>600 kg</t>
+  </si>
+  <si>
+    <t>1200 kg</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>P2, P3</t>
+  </si>
+  <si>
+    <t>P1, P4, Can</t>
+  </si>
+  <si>
+    <t>P1</t>
   </si>
 </sst>
 </file>
@@ -1606,16 +1630,16 @@
         <v>297</v>
       </c>
       <c r="B2" s="10">
-        <v>-2703</v>
+        <v>-2693</v>
       </c>
       <c r="C2" s="10">
-        <v>-584</v>
+        <v>-604</v>
       </c>
       <c r="D2" s="10">
-        <v>-1785</v>
+        <v>-1775</v>
       </c>
       <c r="E2" s="10">
-        <v>1308</v>
+        <v>1288</v>
       </c>
       <c r="F2" s="10" t="s">
         <v>141</v>
@@ -1632,16 +1656,16 @@
         <v>298</v>
       </c>
       <c r="B3" s="10">
-        <v>-1782</v>
+        <v>-1772</v>
       </c>
       <c r="C3" s="10">
-        <v>-194</v>
+        <v>-214</v>
       </c>
       <c r="D3" s="10">
-        <v>-471</v>
+        <v>-461</v>
       </c>
       <c r="E3" s="10">
-        <v>930</v>
+        <v>910</v>
       </c>
       <c r="F3" s="10" t="s">
         <v>295</v>
@@ -1658,16 +1682,16 @@
         <v>299</v>
       </c>
       <c r="B4" s="10">
-        <v>-1782</v>
+        <v>-1772</v>
       </c>
       <c r="C4" s="10">
-        <v>-1300</v>
+        <v>-1320</v>
       </c>
       <c r="D4" s="10">
-        <v>2645</v>
+        <v>2655</v>
       </c>
       <c r="E4" s="10">
-        <v>-194</v>
+        <v>-214</v>
       </c>
       <c r="F4" s="10" t="s">
         <v>296</v>
@@ -1681,16 +1705,16 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B5" s="10">
-        <v>-471</v>
+        <v>-461</v>
       </c>
       <c r="C5" s="10">
-        <v>-194</v>
+        <v>-214</v>
       </c>
       <c r="D5" s="10">
-        <v>880</v>
+        <v>890</v>
       </c>
       <c r="E5" s="10">
-        <v>733</v>
+        <v>713</v>
       </c>
       <c r="F5" s="10" t="s">
         <v>296</v>
@@ -1704,16 +1728,16 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B6" s="10">
-        <v>880</v>
+        <v>890</v>
       </c>
       <c r="C6" s="10">
-        <v>-194</v>
+        <v>-214</v>
       </c>
       <c r="D6" s="10">
-        <v>2644</v>
+        <v>2654</v>
       </c>
       <c r="E6" s="10">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>296</v>
@@ -3544,7 +3568,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9DA2CD0-4EB4-4612-8E4D-C2326FA17524}">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.5546875" style="10" bestFit="1" customWidth="1"/>
@@ -3554,10 +3578,12 @@
     <col min="7" max="7" width="12.44140625" style="10" customWidth="1"/>
     <col min="8" max="8" width="8.88671875" style="10"/>
     <col min="9" max="9" width="66.33203125" style="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="10"/>
+    <col min="10" max="10" width="8.88671875" style="10"/>
+    <col min="11" max="11" width="12" style="10" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -3585,8 +3611,14 @@
       <c r="I1" s="12" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J1" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
         <v>190</v>
       </c>
@@ -3611,8 +3643,14 @@
       <c r="I2" s="10" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J2" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
         <v>191</v>
       </c>
@@ -3637,8 +3675,14 @@
       <c r="I3" s="10" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J3" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
         <v>192</v>
       </c>
@@ -3663,8 +3707,14 @@
       <c r="I4" s="10" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J4" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>193</v>
       </c>
@@ -3689,38 +3739,44 @@
       <c r="I5" s="10" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>147</v>
+      <c r="J5" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" s="10" t="s">
+        <v>305</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="C6">
-        <v>1467</v>
-      </c>
-      <c r="D6">
-        <v>-706</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C6" s="10">
+        <v>778</v>
+      </c>
+      <c r="D6" s="10">
+        <v>-674</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7">
         <v>1467</v>
       </c>
       <c r="D7">
-        <v>-572</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="10" t="s">
-        <v>149</v>
+        <v>-706</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>148</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>188</v>
@@ -3729,12 +3785,12 @@
         <v>1467</v>
       </c>
       <c r="D8">
-        <v>-417</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+        <v>-572</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>188</v>
@@ -3743,20 +3799,34 @@
         <v>1467</v>
       </c>
       <c r="D9">
-        <v>-305</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>146</v>
+        <v>-417</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" s="10" t="s">
+        <v>150</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="10">
+        <v>1467</v>
+      </c>
+      <c r="D10">
+        <v>-305</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>146</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="C11">
         <v>1142</v>
       </c>
-      <c r="D10">
+      <c r="D11">
         <v>-168</v>
       </c>
     </row>
@@ -4939,7 +5009,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.21875" customWidth="1"/>
@@ -5151,24 +5221,21 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>131</v>
-      </c>
-      <c r="B9">
+    <row r="9" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="10">
+        <v>595</v>
+      </c>
+      <c r="C9" s="10">
+        <v>-709</v>
+      </c>
+      <c r="D9" s="10">
         <v>734</v>
       </c>
-      <c r="C9">
-        <v>-956</v>
-      </c>
-      <c r="D9">
-        <v>1331</v>
-      </c>
-      <c r="E9">
-        <v>-796</v>
-      </c>
-      <c r="F9" t="s">
-        <v>139</v>
+      <c r="E9" s="10">
+        <v>-598</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>129</v>
       </c>
       <c r="G9" s="10">
         <v>0.2</v>
@@ -5178,17 +5245,20 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>131</v>
+      </c>
       <c r="B10">
-        <v>1233</v>
+        <v>734</v>
       </c>
       <c r="C10">
-        <v>-1068</v>
+        <v>-956</v>
       </c>
       <c r="D10">
-        <v>1395</v>
+        <v>1331</v>
       </c>
       <c r="E10">
-        <v>-956</v>
+        <v>-796</v>
       </c>
       <c r="F10" t="s">
         <v>139</v>
@@ -5201,23 +5271,20 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>133</v>
-      </c>
       <c r="B11">
-        <v>461</v>
+        <v>1233</v>
       </c>
       <c r="C11">
-        <v>-1182</v>
+        <v>-1068</v>
       </c>
       <c r="D11">
-        <v>734</v>
+        <v>1395</v>
       </c>
       <c r="E11">
-        <v>-711</v>
+        <v>-956</v>
       </c>
       <c r="F11" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="G11" s="10">
         <v>0.2</v>
@@ -5227,23 +5294,23 @@
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" s="10" t="s">
-        <v>135</v>
+      <c r="A12" t="s">
+        <v>133</v>
       </c>
       <c r="B12">
-        <v>2133</v>
+        <v>461</v>
       </c>
       <c r="C12">
-        <v>-1311</v>
+        <v>-1182</v>
       </c>
       <c r="D12">
-        <v>2655</v>
+        <v>734</v>
       </c>
       <c r="E12">
-        <v>186</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>138</v>
+        <v>-711</v>
+      </c>
+      <c r="F12" t="s">
+        <v>134</v>
       </c>
       <c r="G12" s="10">
         <v>0.2</v>
@@ -5253,23 +5320,23 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>136</v>
+      <c r="A13" s="10" t="s">
+        <v>135</v>
       </c>
       <c r="B13">
-        <v>-1772</v>
+        <v>2133</v>
       </c>
       <c r="C13">
-        <v>-1183</v>
+        <v>-1311</v>
       </c>
       <c r="D13">
-        <v>-540</v>
+        <v>2655</v>
       </c>
       <c r="E13">
-        <v>-218</v>
-      </c>
-      <c r="F13" t="s">
-        <v>137</v>
+        <v>186</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>138</v>
       </c>
       <c r="G13" s="10">
         <v>0.2</v>
@@ -5279,22 +5346,22 @@
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" s="10" t="s">
+      <c r="A14" t="s">
         <v>136</v>
       </c>
       <c r="B14">
-        <v>-464</v>
+        <v>-1772</v>
       </c>
       <c r="C14">
         <v>-1183</v>
       </c>
       <c r="D14">
-        <v>461</v>
+        <v>-540</v>
       </c>
       <c r="E14">
         <v>-218</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F14" t="s">
         <v>137</v>
       </c>
       <c r="G14" s="10">
@@ -5305,17 +5372,20 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" s="10" t="s">
+        <v>136</v>
+      </c>
       <c r="B15">
-        <v>1527</v>
+        <v>-464</v>
       </c>
       <c r="C15">
-        <v>-1187</v>
+        <v>-1183</v>
       </c>
       <c r="D15">
-        <v>1924</v>
+        <v>461</v>
       </c>
       <c r="E15">
-        <v>-982</v>
+        <v>-218</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>137</v>
@@ -5328,20 +5398,17 @@
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="B16" s="10">
+      <c r="B16">
         <v>1527</v>
       </c>
       <c r="C16">
+        <v>-1187</v>
+      </c>
+      <c r="D16">
+        <v>1924</v>
+      </c>
+      <c r="E16">
         <v>-982</v>
-      </c>
-      <c r="D16">
-        <v>2126</v>
-      </c>
-      <c r="E16">
-        <v>-6</v>
       </c>
       <c r="F16" s="10" t="s">
         <v>137</v>
@@ -5355,27 +5422,53 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B17" s="10">
-        <v>-2694</v>
-      </c>
-      <c r="C17" s="10">
-        <v>-603</v>
-      </c>
-      <c r="D17" s="10">
-        <v>-1773</v>
-      </c>
-      <c r="E17" s="10">
-        <v>1304</v>
+        <v>1527</v>
+      </c>
+      <c r="C17">
+        <v>-982</v>
+      </c>
+      <c r="D17">
+        <v>2126</v>
+      </c>
+      <c r="E17">
+        <v>-6</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G17" s="10">
         <v>0.2</v>
       </c>
       <c r="H17" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B18" s="10">
+        <v>-2694</v>
+      </c>
+      <c r="C18" s="10">
+        <v>-603</v>
+      </c>
+      <c r="D18" s="10">
+        <v>-1773</v>
+      </c>
+      <c r="E18" s="10">
+        <v>1304</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="G18" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="H18" s="10">
         <v>18</v>
       </c>
     </row>
